--- a/Excel Assignment 1 - Data Exploration.xlsx
+++ b/Excel Assignment 1 - Data Exploration.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bharath\Downloads\Data Analytics\Excel Assignment 1 - Data Exploration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bharath\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D950D544-B905-4E6A-9F59-6E0DF707BF0A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB472AC-7160-408C-B3F8-2F8ABBF75F81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -604,11 +604,17 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color rgb="FF000000"/>
+        <color theme="1"/>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -642,29 +648,69 @@
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
         <top style="thin">
           <color indexed="64"/>
         </top>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -680,7 +726,7 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -688,6 +734,22 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -812,44 +874,6 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFE0F7FA"/>
-          <bgColor rgb="FFE0F7FA"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE0F7FA"/>
@@ -1172,16 +1196,16 @@
     <tableColumn id="4" xr3:uid="{BF7A9B9A-D9A7-4E8B-8611-C8E4503F01DA}" name="Price ($)" dataDxfId="12"/>
     <tableColumn id="5" xr3:uid="{E1034DAC-301B-4F66-9621-45007A9ED2A7}" name="Quantity" dataDxfId="11"/>
     <tableColumn id="6" xr3:uid="{A15F51D7-8575-4260-B8CE-925348587F9A}" name="Category" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{47EDD80A-8BFB-4363-8F3C-E851E7FE3694}" name="Price Range" dataDxfId="9">
-      <calculatedColumnFormula>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{47EDD80A-8BFB-4363-8F3C-E851E7FE3694}" name="Price Range" dataDxfId="0">
+      <calculatedColumnFormula>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E2D7C438-678B-4DF6-8E7E-8E1F4EB8FF01}" name="Day" dataDxfId="8">
+    <tableColumn id="8" xr3:uid="{E2D7C438-678B-4DF6-8E7E-8E1F4EB8FF01}" name="Day" dataDxfId="9">
       <calculatedColumnFormula>LEFT(Table2[[#This Row],[Product ID]],2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{0D09C58B-8A7D-4A3B-BC84-1C7B1C3A5A91}" name=" Country Code" dataDxfId="7">
+    <tableColumn id="13" xr3:uid="{0D09C58B-8A7D-4A3B-BC84-1C7B1C3A5A91}" name=" Country Code" dataDxfId="8">
       <calculatedColumnFormula>RIGHT(Table2[[#This Row],[Product ID]],2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{B2EC366B-A0B4-474F-95EB-D1CF3C568BD8}" name=" Month " dataDxfId="6">
+    <tableColumn id="14" xr3:uid="{B2EC366B-A0B4-474F-95EB-D1CF3C568BD8}" name=" Month " dataDxfId="7">
       <calculatedColumnFormula>MID(Table2[[#This Row],[Product ID]],4,3)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1190,10 +1214,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7BA38F98-D678-4C6C-A457-E938B332306C}" name="Table5" displayName="Table5" ref="K1:L8" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7BA38F98-D678-4C6C-A457-E938B332306C}" name="Table5" displayName="Table5" ref="L1:M8" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DC1103BA-1BB5-4F91-AE9A-A1E0367DE4DB}" name="Basic Data Exploration" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{A2F1A6FF-2D6F-4F4A-A0B6-8874221A4E53}" name="Total" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{DC1103BA-1BB5-4F91-AE9A-A1E0367DE4DB}" name="Basic Data Exploration" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{A2F1A6FF-2D6F-4F4A-A0B6-8874221A4E53}" name="Total" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3115,8 +3139,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9D6D45-EF4A-4E6E-BEB1-C105BE4F40ED}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:L1000"/>
+  <dimension ref="A1:M1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" style="19" bestFit="1" customWidth="1"/>
@@ -3129,10 +3154,11 @@
     <col min="8" max="8" width="9" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.5703125" style="19" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="47.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -3163,14 +3189,14 @@
       <c r="J1" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="L1" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="M1" s="30" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
@@ -3190,7 +3216,7 @@
         <v>9</v>
       </c>
       <c r="G2" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>High Price</v>
       </c>
       <c r="H2" s="23" t="str">
@@ -3205,15 +3231,15 @@
         <f>MID(Table2[[#This Row],[Product ID]],4,3)</f>
         <v>JAN</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="L2" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="L2" s="27">
+      <c r="M2" s="27">
         <f>SUM(Table2[Price ($)])</f>
         <v>10100</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17" t="s">
         <v>10</v>
       </c>
@@ -3233,7 +3259,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H3" s="24" t="str">
@@ -3248,15 +3274,15 @@
         <f>MID(Table2[[#This Row],[Product ID]],4,3)</f>
         <v>FEB</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="L3" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="L3" s="27">
-        <f>COUNTA(Table2[[#All],[Product Name]])</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M3" s="27">
+        <f>COUNTA(Table2[Product Name])</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
         <v>14</v>
       </c>
@@ -3276,7 +3302,7 @@
         <v>17</v>
       </c>
       <c r="G4" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H4" s="23" t="str">
@@ -3291,15 +3317,15 @@
         <f>MID(Table2[[#This Row],[Product ID]],4,3)</f>
         <v>MAR</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="L4" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="L4" s="27">
+      <c r="M4" s="27">
         <f>AVERAGE(Table2[Price ($)])</f>
         <v>297.05882352941177</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>18</v>
       </c>
@@ -3319,7 +3345,7 @@
         <v>9</v>
       </c>
       <c r="G5" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>High Price</v>
       </c>
       <c r="H5" s="24" t="str">
@@ -3334,15 +3360,15 @@
         <f>MID(Table2[[#This Row],[Product ID]],4,3)</f>
         <v>APR</v>
       </c>
-      <c r="K5" s="26" t="s">
+      <c r="L5" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="L5" s="27">
+      <c r="M5" s="27">
         <f>MIN(Table2[Price ($)])</f>
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>21</v>
       </c>
@@ -3362,7 +3388,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H6" s="23" t="str">
@@ -3377,15 +3403,15 @@
         <f>MID(Table2[[#This Row],[Product ID]],4,3)</f>
         <v>MAY</v>
       </c>
-      <c r="K6" s="26" t="s">
+      <c r="L6" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="L6" s="27">
+      <c r="M6" s="27">
         <f>MAX(Table2[Price ($)])</f>
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>25</v>
       </c>
@@ -3405,7 +3431,7 @@
         <v>9</v>
       </c>
       <c r="G7" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H7" s="24" t="str">
@@ -3420,15 +3446,15 @@
         <f>MID(Table2[[#This Row],[Product ID]],4,3)</f>
         <v>JUN</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="L7" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="L7" s="27">
+      <c r="M7" s="27">
         <f>SUMIF(F2:F35,"Electronics",D2:D35)</f>
         <v>8050</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
         <v>28</v>
       </c>
@@ -3448,7 +3474,7 @@
         <v>13</v>
       </c>
       <c r="G8" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H8" s="23" t="str">
@@ -3463,15 +3489,15 @@
         <f>MID(Table2[[#This Row],[Product ID]],4,3)</f>
         <v>JUL</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="L8" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="L8" s="29">
+      <c r="M8" s="29">
         <f>COUNTIF(Table2[Price ($)],"&lt;100")</f>
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>31</v>
       </c>
@@ -3491,7 +3517,7 @@
         <v>17</v>
       </c>
       <c r="G9" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H9" s="24" t="str">
@@ -3507,7 +3533,7 @@
         <v>AUG</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
         <v>34</v>
       </c>
@@ -3527,8 +3553,8 @@
         <v>9</v>
       </c>
       <c r="G10" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
-        <v>Standard Price</v>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
+        <v>High Price</v>
       </c>
       <c r="H10" s="23" t="str">
         <f>LEFT(Table2[[#This Row],[Product ID]],2)</f>
@@ -3543,7 +3569,7 @@
         <v>SEP</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>37</v>
       </c>
@@ -3563,7 +3589,7 @@
         <v>24</v>
       </c>
       <c r="G11" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H11" s="24" t="str">
@@ -3579,7 +3605,7 @@
         <v>OCT</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
         <v>40</v>
       </c>
@@ -3599,7 +3625,7 @@
         <v>9</v>
       </c>
       <c r="G12" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>High Price</v>
       </c>
       <c r="H12" s="23" t="str">
@@ -3615,7 +3641,7 @@
         <v>JUN</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
         <v>42</v>
       </c>
@@ -3635,7 +3661,7 @@
         <v>13</v>
       </c>
       <c r="G13" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H13" s="24" t="str">
@@ -3651,7 +3677,7 @@
         <v>NOV</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>43</v>
       </c>
@@ -3671,7 +3697,7 @@
         <v>17</v>
       </c>
       <c r="G14" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H14" s="23" t="str">
@@ -3687,7 +3713,7 @@
         <v>DEC</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="17" t="s">
         <v>45</v>
       </c>
@@ -3707,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="G15" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H15" s="24" t="str">
@@ -3723,7 +3749,7 @@
         <v>FEB</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>48</v>
       </c>
@@ -3743,7 +3769,7 @@
         <v>9</v>
       </c>
       <c r="G16" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H16" s="23" t="str">
@@ -3779,7 +3805,7 @@
         <v>53</v>
       </c>
       <c r="G17" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H17" s="24" t="str">
@@ -3815,7 +3841,7 @@
         <v>9</v>
       </c>
       <c r="G18" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H18" s="23" t="str">
@@ -3851,7 +3877,7 @@
         <v>9</v>
       </c>
       <c r="G19" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>High Price</v>
       </c>
       <c r="H19" s="24" t="str">
@@ -3887,7 +3913,7 @@
         <v>13</v>
       </c>
       <c r="G20" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H20" s="23" t="str">
@@ -3923,7 +3949,7 @@
         <v>24</v>
       </c>
       <c r="G21" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H21" s="24" t="str">
@@ -3959,7 +3985,7 @@
         <v>9</v>
       </c>
       <c r="G22" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>High Price</v>
       </c>
       <c r="H22" s="23" t="str">
@@ -3995,7 +4021,7 @@
         <v>17</v>
       </c>
       <c r="G23" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H23" s="24" t="str">
@@ -4031,7 +4057,7 @@
         <v>9</v>
       </c>
       <c r="G24" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H24" s="23" t="str">
@@ -4067,7 +4093,7 @@
         <v>53</v>
       </c>
       <c r="G25" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H25" s="24" t="str">
@@ -4103,7 +4129,7 @@
         <v>9</v>
       </c>
       <c r="G26" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>High Price</v>
       </c>
       <c r="H26" s="23" t="str">
@@ -4139,7 +4165,7 @@
         <v>13</v>
       </c>
       <c r="G27" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H27" s="24" t="str">
@@ -4175,7 +4201,7 @@
         <v>17</v>
       </c>
       <c r="G28" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H28" s="23" t="str">
@@ -4211,7 +4237,7 @@
         <v>9</v>
       </c>
       <c r="G29" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H29" s="24" t="str">
@@ -4247,7 +4273,7 @@
         <v>13</v>
       </c>
       <c r="G30" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H30" s="23" t="str">
@@ -4283,7 +4309,7 @@
         <v>17</v>
       </c>
       <c r="G31" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H31" s="24" t="str">
@@ -4319,7 +4345,7 @@
         <v>9</v>
       </c>
       <c r="G32" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H32" s="23" t="str">
@@ -4355,7 +4381,7 @@
         <v>13</v>
       </c>
       <c r="G33" s="9" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H33" s="24" t="str">
@@ -4391,7 +4417,7 @@
         <v>9</v>
       </c>
       <c r="G34" s="8" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>High Price</v>
       </c>
       <c r="H34" s="23" t="str">
@@ -4427,7 +4453,7 @@
         <v>53</v>
       </c>
       <c r="G35" s="14" t="str">
-        <f>IF(Table2[[#This Row],[Price ($)]]&gt;500,"High Price","Standard Price")</f>
+        <f>IF(Table2[[#This Row],[Price ($)]]&gt;=500,"High Price","Standard Price")</f>
         <v>Standard Price</v>
       </c>
       <c r="H35" s="25" t="str">
@@ -5410,6 +5436,30 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <conditionalFormatting sqref="G1:G1048576">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF008AEF"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{3B83DE38-FEB7-40AE-8CF1-E3C236113203}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:J1048576">
     <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="min"/>
@@ -5418,7 +5468,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3B83DE38-FEB7-40AE-8CF1-E3C236113203}</x14:id>
+          <x14:id>{5D01E743-6BE0-49AC-B3AD-61420F2971D8}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5433,53 +5483,25 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:J1048576">
-    <cfRule type="dataBar" priority="4">
+  <conditionalFormatting sqref="M2:M8">
+    <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FF008AEF"/>
+        <color rgb="FF63C384"/>
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{5D01E743-6BE0-49AC-B3AD-61420F2971D8}</x14:id>
+          <x14:id>{71B7DCB1-30FD-4C4D-8DCB-4D407BAFEC77}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L8">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFCFCFF"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="iconSet" priority="2">
-      <iconSet iconSet="5Rating">
-        <cfvo type="percent" val="0"/>
-        <cfvo type="percent" val="20"/>
-        <cfvo type="percent" val="40"/>
-        <cfvo type="percent" val="60"/>
-        <cfvo type="percent" val="80"/>
-      </iconSet>
-    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -5510,6 +5532,19 @@
           </x14:cfRule>
           <xm:sqref>H1:J1048576</xm:sqref>
         </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{71B7DCB1-30FD-4C4D-8DCB-4D407BAFEC77}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>M2:M8</xm:sqref>
+        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>
